--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -23744,7 +23744,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -27915,7 +27915,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30200,7 +30200,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33283,7 +33283,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39050,7 +39050,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -40936,7 +40936,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42423,7 +42423,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -44708,7 +44708,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -45107,7 +45107,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47791,7 +47791,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -48589,7 +48589,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -49677,7 +49677,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -50076,7 +50076,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -50475,7 +50475,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -50874,7 +50874,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -51814,7 +51814,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -52760,7 +52760,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -53159,7 +53159,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -53558,7 +53558,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -54646,7 +54646,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -55444,7 +55444,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -55843,7 +55843,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -56931,7 +56931,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -57330,7 +57330,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -57729,7 +57729,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -58128,7 +58128,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -59068,7 +59068,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -59615,7 +59615,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -60014,7 +60014,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -60413,7 +60413,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -60812,7 +60812,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -61900,7 +61900,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -62299,7 +62299,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -62698,7 +62698,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -63097,7 +63097,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -64185,7 +64185,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -64584,7 +64584,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -64983,7 +64983,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -65382,7 +65382,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -66470,7 +66470,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -66869,7 +66869,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -67268,7 +67268,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -68066,7 +68066,7 @@
       </c>
       <c r="AJ367" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK367" t="inlineStr">
@@ -69154,7 +69154,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -69553,7 +69553,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -69952,7 +69952,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -70351,7 +70351,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -71439,7 +71439,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -71838,7 +71838,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -72237,7 +72237,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
@@ -72636,7 +72636,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -73576,7 +73576,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -74123,7 +74123,7 @@
       </c>
       <c r="AJ399" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK399" t="inlineStr">
@@ -74522,7 +74522,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -74921,7 +74921,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -75320,7 +75320,7 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
@@ -76408,7 +76408,7 @@
       </c>
       <c r="AJ411" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK411" t="inlineStr">
@@ -76807,7 +76807,7 @@
       </c>
       <c r="AJ413" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK413" t="inlineStr">
@@ -77206,7 +77206,7 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
@@ -77605,7 +77605,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -78693,7 +78693,7 @@
       </c>
       <c r="AJ423" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK423" t="inlineStr">
@@ -79092,7 +79092,7 @@
       </c>
       <c r="AJ425" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK425" t="inlineStr">
@@ -79491,7 +79491,7 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
@@ -79890,7 +79890,7 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
@@ -80289,7 +80289,7 @@
       </c>
       <c r="AJ431" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK431" t="inlineStr">
@@ -81377,7 +81377,7 @@
       </c>
       <c r="AJ437" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK437" t="inlineStr">
@@ -81776,7 +81776,7 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
@@ -82175,7 +82175,7 @@
       </c>
       <c r="AJ441" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK441" t="inlineStr">
@@ -82574,7 +82574,7 @@
       </c>
       <c r="AJ443" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK443" t="inlineStr">
@@ -83662,7 +83662,7 @@
       </c>
       <c r="AJ449" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK449" t="inlineStr">
@@ -84061,7 +84061,7 @@
       </c>
       <c r="AJ451" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK451" t="inlineStr">
@@ -84460,7 +84460,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -84859,7 +84859,7 @@
       </c>
       <c r="AJ455" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK455" t="inlineStr">
@@ -85947,7 +85947,7 @@
       </c>
       <c r="AJ461" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK461" t="inlineStr">
@@ -86346,7 +86346,7 @@
       </c>
       <c r="AJ463" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK463" t="inlineStr">
@@ -86745,7 +86745,7 @@
       </c>
       <c r="AJ465" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK465" t="inlineStr">
@@ -87144,7 +87144,7 @@
       </c>
       <c r="AJ467" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK467" t="inlineStr">
@@ -87543,7 +87543,7 @@
       </c>
       <c r="AJ469" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK469" t="inlineStr">
@@ -88631,7 +88631,7 @@
       </c>
       <c r="AJ475" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK475" t="inlineStr">
@@ -89030,7 +89030,7 @@
       </c>
       <c r="AJ477" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK477" t="inlineStr">
@@ -89429,7 +89429,7 @@
       </c>
       <c r="AJ479" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK479" t="inlineStr">
@@ -89828,7 +89828,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">

--- a/diseases/d165/2010-2014.xlsx
+++ b/diseases/d165/2010-2014.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1858,6 +1868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2006,6 +2021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2547,6 +2567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2695,6 +2720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3236,6 +3266,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3384,6 +3419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3925,6 +3965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4073,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4614,6 +4664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4762,6 +4817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5303,6 +5363,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5451,6 +5516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5992,6 +6062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6140,6 +6215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6681,6 +6761,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6829,6 +6914,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7370,6 +7460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7518,6 +7613,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8059,6 +8159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8207,6 +8312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8748,6 +8858,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8896,6 +9011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9437,6 +9557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9585,6 +9710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10126,6 +10256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10274,6 +10409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10815,6 +10955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10963,6 +11108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11504,6 +11654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11652,6 +11807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12193,6 +12353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12341,6 +12506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12882,6 +13052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13030,6 +13205,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13571,6 +13751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13719,6 +13904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14260,6 +14450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14408,6 +14603,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14949,6 +15149,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15097,6 +15302,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15638,6 +15848,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15786,6 +16001,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16327,6 +16547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16475,6 +16700,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17016,6 +17246,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17164,6 +17399,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17705,6 +17945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17853,6 +18098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18394,6 +18644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18542,6 +18797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19083,6 +19343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19231,6 +19496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19772,6 +20042,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19920,6 +20195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20461,6 +20741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20609,6 +20894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21150,6 +21440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21298,6 +21593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21839,6 +22139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21987,6 +22292,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22528,6 +22838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22676,6 +22991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23217,6 +23537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23365,6 +23690,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25103,6 +25433,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25251,6 +25586,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27388,6 +27728,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27536,6 +27881,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29673,6 +30023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29821,6 +30176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32357,6 +32717,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32505,6 +32870,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34642,6 +35012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34790,6 +35165,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36927,6 +37307,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37075,6 +37460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39611,6 +40001,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39759,6 +40154,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41896,6 +42296,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42044,6 +42449,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44181,6 +44591,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44329,6 +44744,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46865,6 +47285,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47013,6 +47438,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49150,6 +49580,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49298,6 +49733,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51435,6 +51875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51982,6 +52427,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54119,6 +54569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54267,6 +54722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56404,6 +56864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56552,6 +57017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58689,6 +59159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59236,6 +59711,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61373,6 +61853,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61521,6 +62006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63658,6 +64148,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63806,6 +64301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65943,6 +66443,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66091,6 +66596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68627,6 +69137,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68775,6 +69290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70912,6 +71432,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71060,6 +71585,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73197,6 +73727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73744,6 +74279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75881,6 +76421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76029,6 +76574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78166,6 +78716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78314,6 +78869,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -80850,6 +81410,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -80998,6 +81563,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -83135,6 +83705,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -83283,6 +83858,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -85420,6 +86000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO458" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -85568,6 +86153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO459" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -88104,6 +88694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO472" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -88250,6 +88845,11 @@
       <c r="S473" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO473" t="inlineStr">
